--- a/Excel_MOD/spreadsheet_template_.xlsx
+++ b/Excel_MOD/spreadsheet_template_.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11114"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Drew\PycharmProjects\Excel_MOD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/drewfoster/Desktop/Excel_Automator/Excel-Automator/Excel_MOD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F5BD79-91C5-454C-921A-212194913EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC289E6A-7675-9B4C-B0AA-B3F1E9FB5AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2355" yWindow="45" windowWidth="23250" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -8314,51 +8314,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AP489"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="26.83203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="27.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8486,7 +8485,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
         <v>1654</v>
       </c>
@@ -8608,7 +8607,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A3" s="27" t="s">
         <v>1888</v>
       </c>
@@ -8730,7 +8729,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A4" s="27" t="s">
         <v>2573</v>
       </c>
@@ -8852,7 +8851,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="24" t="s">
         <v>2499</v>
       </c>
@@ -8972,7 +8971,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A6" s="24" t="s">
         <v>2559</v>
       </c>
@@ -9092,7 +9091,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A7" s="24" t="s">
         <v>2499</v>
       </c>
@@ -9214,7 +9213,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
         <v>2559</v>
       </c>
@@ -9336,7 +9335,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>681</v>
       </c>
@@ -9458,7 +9457,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>732</v>
       </c>
@@ -9578,7 +9577,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A11" s="24" t="s">
         <v>1304</v>
       </c>
@@ -9698,7 +9697,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="12" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A12" s="24" t="s">
         <v>1341</v>
       </c>
@@ -9818,7 +9817,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="13" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A13" s="36" t="s">
         <v>1924</v>
       </c>
@@ -9940,7 +9939,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A14" s="27" t="s">
         <v>2274</v>
       </c>
@@ -10064,7 +10063,7 @@
         <v>2282</v>
       </c>
     </row>
-    <row r="15" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>818</v>
       </c>
@@ -10184,7 +10183,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="16" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>829</v>
       </c>
@@ -10302,7 +10301,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="17" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
         <v>2499</v>
       </c>
@@ -10424,7 +10423,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A18" s="24" t="s">
         <v>2559</v>
       </c>
@@ -10546,7 +10545,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="19" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A19" s="21" t="s">
         <v>1154</v>
       </c>
@@ -10662,7 +10661,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="20" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A20" s="21" t="s">
         <v>1154</v>
       </c>
@@ -10778,7 +10777,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="21" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>175</v>
       </c>
@@ -10898,7 +10897,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>221</v>
       </c>
@@ -11020,7 +11019,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>393</v>
       </c>
@@ -11142,7 +11141,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A24" s="24" t="s">
         <v>1150</v>
       </c>
@@ -11262,7 +11261,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="25" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>692</v>
       </c>
@@ -11382,7 +11381,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A26" s="24" t="s">
         <v>1157</v>
       </c>
@@ -11500,7 +11499,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="27" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
         <v>1160</v>
       </c>
@@ -11618,7 +11617,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="28" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A28" s="24" t="s">
         <v>1239</v>
       </c>
@@ -11738,7 +11737,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="29" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A29" s="24" t="s">
         <v>1241</v>
       </c>
@@ -11858,7 +11857,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="30" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A30" s="24" t="s">
         <v>1243</v>
       </c>
@@ -11978,7 +11977,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="31" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A31" s="24" t="s">
         <v>1245</v>
       </c>
@@ -12096,7 +12095,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="32" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A32" s="24" t="s">
         <v>1247</v>
       </c>
@@ -12214,7 +12213,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="33" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A33" s="24" t="s">
         <v>1249</v>
       </c>
@@ -12332,7 +12331,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="34" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A34" s="24" t="s">
         <v>1251</v>
       </c>
@@ -12450,7 +12449,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="35" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A35" s="36" t="s">
         <v>1253</v>
       </c>
@@ -12570,7 +12569,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="36" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A36" s="24" t="s">
         <v>1261</v>
       </c>
@@ -12688,7 +12687,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="37" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A37" s="24" t="s">
         <v>1302</v>
       </c>
@@ -12808,7 +12807,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="38" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A38" s="24" t="s">
         <v>2219</v>
       </c>
@@ -12930,7 +12929,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="39" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A39" s="24" t="s">
         <v>2222</v>
       </c>
@@ -13050,7 +13049,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="40" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A40" s="24" t="s">
         <v>2226</v>
       </c>
@@ -13168,7 +13167,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="41" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A41" s="24" t="s">
         <v>2228</v>
       </c>
@@ -13286,7 +13285,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="42" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A42" s="24" t="s">
         <v>2230</v>
       </c>
@@ -13404,7 +13403,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="43" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A43" s="24" t="s">
         <v>2232</v>
       </c>
@@ -13522,7 +13521,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="44" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A44" s="24" t="s">
         <v>2234</v>
       </c>
@@ -13642,7 +13641,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="45" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A45" s="24" t="s">
         <v>2236</v>
       </c>
@@ -13762,7 +13761,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="46" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A46" s="24" t="s">
         <v>1046</v>
       </c>
@@ -13882,7 +13881,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="47" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A47" s="24" t="s">
         <v>1143</v>
       </c>
@@ -14002,7 +14001,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="48" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A48" s="24" t="s">
         <v>1146</v>
       </c>
@@ -14122,7 +14121,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="49" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A49" s="24" t="s">
         <v>1150</v>
       </c>
@@ -14242,7 +14241,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="50" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>213</v>
       </c>
@@ -14360,7 +14359,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A51" s="24" t="s">
         <v>1160</v>
       </c>
@@ -14478,7 +14477,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="52" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A52" s="24" t="s">
         <v>1166</v>
       </c>
@@ -14598,7 +14597,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="53" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A53" s="24" t="s">
         <v>1239</v>
       </c>
@@ -14718,7 +14717,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="54" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A54" s="24" t="s">
         <v>1241</v>
       </c>
@@ -14838,7 +14837,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="55" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A55" s="24" t="s">
         <v>1243</v>
       </c>
@@ -14958,7 +14957,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="56" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A56" s="24" t="s">
         <v>1245</v>
       </c>
@@ -15076,7 +15075,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="57" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A57" s="24" t="s">
         <v>1247</v>
       </c>
@@ -15194,7 +15193,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="58" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A58" s="24" t="s">
         <v>1251</v>
       </c>
@@ -15312,7 +15311,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="59" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A59" s="24" t="s">
         <v>1261</v>
       </c>
@@ -15430,7 +15429,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="60" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A60" s="24" t="s">
         <v>1292</v>
       </c>
@@ -15550,7 +15549,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="61" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A61" s="24" t="s">
         <v>1294</v>
       </c>
@@ -15668,7 +15667,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="62" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A62" s="24" t="s">
         <v>1296</v>
       </c>
@@ -15786,7 +15785,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="63" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A63" s="24" t="s">
         <v>1298</v>
       </c>
@@ -15904,7 +15903,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="64" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A64" s="24" t="s">
         <v>1300</v>
       </c>
@@ -16022,7 +16021,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="65" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A65" s="24" t="s">
         <v>1302</v>
       </c>
@@ -16142,7 +16141,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="66" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A66" s="24" t="s">
         <v>2222</v>
       </c>
@@ -16262,7 +16261,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="67" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A67" s="24" t="s">
         <v>2224</v>
       </c>
@@ -16382,7 +16381,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="68" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A68" s="24" t="s">
         <v>2226</v>
       </c>
@@ -16500,7 +16499,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="69" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A69" s="24" t="s">
         <v>2228</v>
       </c>
@@ -16618,7 +16617,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="70" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A70" s="24" t="s">
         <v>2230</v>
       </c>
@@ -16736,7 +16735,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="71" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A71" s="24" t="s">
         <v>2234</v>
       </c>
@@ -16856,7 +16855,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="72" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A72" s="24" t="s">
         <v>2236</v>
       </c>
@@ -16976,7 +16975,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="73" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A73" s="24" t="s">
         <v>1411</v>
       </c>
@@ -17098,7 +17097,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="74" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A74" s="36" t="s">
         <v>1675</v>
       </c>
@@ -17220,7 +17219,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="75" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A75" s="27" t="s">
         <v>1682</v>
       </c>
@@ -17342,7 +17341,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="76" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A76" s="36" t="s">
         <v>1958</v>
       </c>
@@ -17464,7 +17463,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="77" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A77" s="36" t="s">
         <v>2042</v>
       </c>
@@ -17586,7 +17585,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="78" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A78" s="36" t="s">
         <v>2086</v>
       </c>
@@ -17708,7 +17707,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="79" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A79" s="27" t="s">
         <v>2163</v>
       </c>
@@ -17830,7 +17829,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="80" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A80" s="24" t="s">
         <v>2452</v>
       </c>
@@ -17952,7 +17951,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="81" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A81" s="36" t="s">
         <v>2459</v>
       </c>
@@ -18074,7 +18073,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="82" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>256</v>
       </c>
@@ -18194,7 +18193,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="83" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A83" s="12" t="s">
         <v>312</v>
       </c>
@@ -18314,7 +18313,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="84" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>379</v>
       </c>
@@ -18432,7 +18431,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="85" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A85" s="12" t="s">
         <v>385</v>
       </c>
@@ -18550,7 +18549,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="86" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A86" s="24" t="s">
         <v>1411</v>
       </c>
@@ -18672,7 +18671,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="87" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A87" s="36" t="s">
         <v>1481</v>
       </c>
@@ -18794,7 +18793,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="88" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A88" s="36" t="s">
         <v>1508</v>
       </c>
@@ -18916,7 +18915,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="89" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A89" s="36" t="s">
         <v>1565</v>
       </c>
@@ -19038,7 +19037,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="90" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A90" s="24" t="s">
         <v>1411</v>
       </c>
@@ -19160,7 +19159,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="91" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A91" s="27" t="s">
         <v>1425</v>
       </c>
@@ -19284,7 +19283,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="92" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A92" s="36" t="s">
         <v>1432</v>
       </c>
@@ -19406,7 +19405,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="93" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A93" s="27" t="s">
         <v>1439</v>
       </c>
@@ -19528,7 +19527,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="94" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A94" s="27" t="s">
         <v>1488</v>
       </c>
@@ -19650,7 +19649,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="95" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A95" s="27" t="s">
         <v>1501</v>
       </c>
@@ -19772,7 +19771,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="96" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A96" s="27" t="s">
         <v>1515</v>
       </c>
@@ -19894,7 +19893,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="97" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A97" s="36" t="s">
         <v>1533</v>
       </c>
@@ -20016,7 +20015,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="98" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A98" s="27" t="s">
         <v>1585</v>
       </c>
@@ -20138,7 +20137,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="99" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A99" s="36" t="s">
         <v>1611</v>
       </c>
@@ -20260,7 +20259,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="100" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A100" s="36" t="s">
         <v>1635</v>
       </c>
@@ -20382,7 +20381,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="101" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A101" s="27" t="s">
         <v>1760</v>
       </c>
@@ -20504,7 +20503,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="102" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A102" s="36" t="s">
         <v>1811</v>
       </c>
@@ -20626,7 +20625,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="103" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A103" s="36" t="s">
         <v>1970</v>
       </c>
@@ -20748,7 +20747,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="104" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A104" s="27" t="s">
         <v>1989</v>
       </c>
@@ -20870,7 +20869,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="105" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A105" s="27" t="s">
         <v>2044</v>
       </c>
@@ -20992,7 +20991,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="106" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A106" s="27" t="s">
         <v>2092</v>
       </c>
@@ -21114,7 +21113,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="107" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A107" s="36" t="s">
         <v>2099</v>
       </c>
@@ -21236,7 +21235,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="108" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A108" s="36" t="s">
         <v>2247</v>
       </c>
@@ -21360,7 +21359,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="109" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A109" s="27" t="s">
         <v>2267</v>
       </c>
@@ -21482,7 +21481,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="110" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A110" s="36" t="s">
         <v>2349</v>
       </c>
@@ -21604,7 +21603,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="111" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A111" s="24" t="s">
         <v>2452</v>
       </c>
@@ -21726,7 +21725,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="112" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A112" s="27" t="s">
         <v>2520</v>
       </c>
@@ -21848,7 +21847,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="113" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>448</v>
       </c>
@@ -21968,7 +21967,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="114" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A114" s="12" t="s">
         <v>455</v>
       </c>
@@ -22088,7 +22087,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="115" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>462</v>
       </c>
@@ -22206,7 +22205,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="116" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>468</v>
       </c>
@@ -22324,7 +22323,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="117" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A117" s="36" t="s">
         <v>1070</v>
       </c>
@@ -22440,7 +22439,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="118" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A118" s="24" t="s">
         <v>1090</v>
       </c>
@@ -22556,7 +22555,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="119" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A119" s="24" t="s">
         <v>1223</v>
       </c>
@@ -22672,7 +22671,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="120" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A120" s="24" t="s">
         <v>1227</v>
       </c>
@@ -22788,7 +22787,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="121" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A121" s="24" t="s">
         <v>1233</v>
       </c>
@@ -22904,7 +22903,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="122" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A122" s="24" t="s">
         <v>1270</v>
       </c>
@@ -23020,7 +23019,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="123" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A123" s="27" t="s">
         <v>1521</v>
       </c>
@@ -23142,7 +23141,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="124" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A124" s="36" t="s">
         <v>1729</v>
       </c>
@@ -23264,7 +23263,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="125" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A125" s="36" t="s">
         <v>1900</v>
       </c>
@@ -23386,7 +23385,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="126" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A126" s="27" t="s">
         <v>1905</v>
       </c>
@@ -23510,7 +23509,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="127" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A127" s="36" t="s">
         <v>2028</v>
       </c>
@@ -23632,7 +23631,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="128" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A128" s="24" t="s">
         <v>2141</v>
       </c>
@@ -23748,7 +23747,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="129" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A129" s="24" t="s">
         <v>2143</v>
       </c>
@@ -23864,7 +23863,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="130" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A130" s="24" t="s">
         <v>2154</v>
       </c>
@@ -23980,7 +23979,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="131" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A131" s="24" t="s">
         <v>2158</v>
       </c>
@@ -24098,7 +24097,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="132" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A132" s="27" t="s">
         <v>2379</v>
       </c>
@@ -24220,7 +24219,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="133" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A133" s="24" t="s">
         <v>1090</v>
       </c>
@@ -24336,7 +24335,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="134" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A134" s="24" t="s">
         <v>1223</v>
       </c>
@@ -24452,7 +24451,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="135" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A135" s="24" t="s">
         <v>1227</v>
       </c>
@@ -24568,7 +24567,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="136" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A136" s="24" t="s">
         <v>1233</v>
       </c>
@@ -24684,7 +24683,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="137" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A137" s="36" t="s">
         <v>1453</v>
       </c>
@@ -24806,7 +24805,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="138" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A138" s="27" t="s">
         <v>1460</v>
       </c>
@@ -24928,7 +24927,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="139" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A139" s="36" t="s">
         <v>1661</v>
       </c>
@@ -25052,7 +25051,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="140" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A140" s="36" t="s">
         <v>1911</v>
       </c>
@@ -25174,7 +25173,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="141" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A141" s="27" t="s">
         <v>2169</v>
       </c>
@@ -25296,7 +25295,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="142" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A142" s="36" t="s">
         <v>2175</v>
       </c>
@@ -25418,7 +25417,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="143" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
         <v>475</v>
       </c>
@@ -25538,7 +25537,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="144" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A144" s="27" t="s">
         <v>1279</v>
       </c>
@@ -25654,7 +25653,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="145" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A145" s="36" t="s">
         <v>1798</v>
       </c>
@@ -25776,7 +25775,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="146" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A146" s="27" t="s">
         <v>1850</v>
       </c>
@@ -25898,7 +25897,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="147" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A147" s="24" t="s">
         <v>2141</v>
       </c>
@@ -26014,7 +26013,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="148" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A148" s="24" t="s">
         <v>2143</v>
       </c>
@@ -26130,7 +26129,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="149" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A149" s="24" t="s">
         <v>2156</v>
       </c>
@@ -26246,7 +26245,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="150" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A150" s="24" t="s">
         <v>2158</v>
       </c>
@@ -26364,7 +26363,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="151" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A151" s="36" t="s">
         <v>2446</v>
       </c>
@@ -26486,7 +26485,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="152" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A152" s="24" t="s">
         <v>1343</v>
       </c>
@@ -26608,7 +26607,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="153" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A153" s="36" t="s">
         <v>1591</v>
       </c>
@@ -26730,7 +26729,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="154" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A154" s="27" t="s">
         <v>1604</v>
       </c>
@@ -26852,7 +26851,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="155" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A155" s="36" t="s">
         <v>1689</v>
       </c>
@@ -26974,7 +26973,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="156" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A156" s="27" t="s">
         <v>1716</v>
       </c>
@@ -27096,7 +27095,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="157" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A157" s="36" t="s">
         <v>1722</v>
       </c>
@@ -27218,7 +27217,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="158" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A158" s="36" t="s">
         <v>1734</v>
       </c>
@@ -27340,7 +27339,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="159" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A159" s="27" t="s">
         <v>1817</v>
       </c>
@@ -27462,7 +27461,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="160" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A160" s="36" t="s">
         <v>1837</v>
       </c>
@@ -27584,7 +27583,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="161" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A161" s="36" t="s">
         <v>1983</v>
       </c>
@@ -27706,7 +27705,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="162" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A162" s="36" t="s">
         <v>1996</v>
       </c>
@@ -27828,7 +27827,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="163" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A163" s="27" t="s">
         <v>2003</v>
       </c>
@@ -27950,7 +27949,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="164" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A164" s="36" t="s">
         <v>2010</v>
       </c>
@@ -28072,7 +28071,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="165" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A165" s="27" t="s">
         <v>2016</v>
       </c>
@@ -28194,7 +28193,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="166" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A166" s="36" t="s">
         <v>2051</v>
       </c>
@@ -28316,7 +28315,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="167" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A167" s="27" t="s">
         <v>2205</v>
       </c>
@@ -28438,7 +28437,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="168" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A168" s="36" t="s">
         <v>2212</v>
       </c>
@@ -28562,7 +28561,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="169" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A169" s="36" t="s">
         <v>2289</v>
       </c>
@@ -28684,7 +28683,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="170" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A170" s="36" t="s">
         <v>2309</v>
       </c>
@@ -28806,7 +28805,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="171" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A171" s="24" t="s">
         <v>2342</v>
       </c>
@@ -28928,7 +28927,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="172" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A172" s="36" t="s">
         <v>2513</v>
       </c>
@@ -29050,7 +29049,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="173" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A173" s="12" t="s">
         <v>490</v>
       </c>
@@ -29170,7 +29169,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="174" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
         <v>507</v>
       </c>
@@ -29288,7 +29287,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="175" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A175" s="12" t="s">
         <v>513</v>
       </c>
@@ -29408,7 +29407,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="176" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
         <v>613</v>
       </c>
@@ -29528,7 +29527,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="177" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
         <v>627</v>
       </c>
@@ -29648,7 +29647,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="178" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
         <v>635</v>
       </c>
@@ -29766,7 +29765,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="179" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A179" s="24" t="s">
         <v>1343</v>
       </c>
@@ -29888,7 +29887,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="180" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A180" s="36" t="s">
         <v>1494</v>
       </c>
@@ -30010,7 +30009,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="181" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A181" s="27" t="s">
         <v>1667</v>
       </c>
@@ -30132,7 +30131,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="182" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A182" s="36" t="s">
         <v>1710</v>
       </c>
@@ -30254,7 +30253,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="183" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A183" s="36" t="s">
         <v>1748</v>
       </c>
@@ -30376,7 +30375,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="184" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A184" s="36" t="s">
         <v>1775</v>
       </c>
@@ -30500,7 +30499,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="185" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A185" s="27" t="s">
         <v>1831</v>
       </c>
@@ -30622,7 +30621,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="186" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A186" s="27" t="s">
         <v>1964</v>
       </c>
@@ -30744,7 +30743,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="187" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A187" s="27" t="s">
         <v>1976</v>
       </c>
@@ -30866,7 +30865,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="188" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A188" s="36" t="s">
         <v>2283</v>
       </c>
@@ -30988,7 +30987,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="189" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A189" s="24" t="s">
         <v>2342</v>
       </c>
@@ -31110,7 +31109,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="190" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A190" s="27" t="s">
         <v>2418</v>
       </c>
@@ -31232,7 +31231,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="191" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A191" s="24" t="s">
         <v>1343</v>
       </c>
@@ -31354,7 +31353,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="192" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A192" s="36" t="s">
         <v>2424</v>
       </c>
@@ -31476,7 +31475,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="193" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A193" s="36" t="s">
         <v>1527</v>
       </c>
@@ -31598,7 +31597,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="194" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A194" s="36" t="s">
         <v>1642</v>
       </c>
@@ -31722,7 +31721,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="195" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A195" s="27" t="s">
         <v>1649</v>
       </c>
@@ -31844,7 +31843,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="196" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A196" s="27" t="s">
         <v>1741</v>
       </c>
@@ -31966,7 +31965,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="197" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A197" s="36" t="s">
         <v>1767</v>
       </c>
@@ -32090,7 +32089,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="198" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A198" s="27" t="s">
         <v>1930</v>
       </c>
@@ -32212,7 +32211,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="199" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A199" s="27" t="s">
         <v>1937</v>
       </c>
@@ -32334,7 +32333,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="200" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A200" s="27" t="s">
         <v>2058</v>
       </c>
@@ -32458,7 +32457,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="201" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A201" s="36" t="s">
         <v>2373</v>
       </c>
@@ -32580,7 +32579,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="202" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A202" s="27" t="s">
         <v>2385</v>
       </c>
@@ -32702,7 +32701,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="203" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A203" s="36" t="s">
         <v>2473</v>
       </c>
@@ -32824,7 +32823,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="204" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A204" s="12" t="s">
         <v>641</v>
       </c>
@@ -32944,7 +32943,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="205" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
         <v>647</v>
       </c>
@@ -33062,7 +33061,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="206" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A206" s="24" t="s">
         <v>1343</v>
       </c>
@@ -33184,7 +33183,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="207" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A207" s="27" t="s">
         <v>1540</v>
       </c>
@@ -33306,7 +33305,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="208" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A208" s="12" t="s">
         <v>653</v>
       </c>
@@ -33426,7 +33425,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="209" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A209" s="36" t="s">
         <v>1783</v>
       </c>
@@ -33548,7 +33547,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="210" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A210" s="24" t="s">
         <v>1343</v>
       </c>
@@ -33670,7 +33669,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="211" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
         <v>660</v>
       </c>
@@ -33788,7 +33787,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="212" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A212" s="24" t="s">
         <v>1128</v>
       </c>
@@ -33906,7 +33905,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="213" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A213" s="36" t="s">
         <v>1140</v>
       </c>
@@ -34024,7 +34023,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="214" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A214" s="36" t="s">
         <v>1555</v>
       </c>
@@ -34148,7 +34147,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="215" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A215" s="27" t="s">
         <v>2553</v>
       </c>
@@ -34270,7 +34269,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="216" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A216" s="12" t="s">
         <v>712</v>
       </c>
@@ -34390,7 +34389,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="217" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
         <v>726</v>
       </c>
@@ -34510,7 +34509,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="218" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A218" s="12" t="s">
         <v>1220</v>
       </c>
@@ -34624,7 +34623,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="219" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A219" s="3" t="s">
         <v>1265</v>
       </c>
@@ -34740,7 +34739,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="220" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A220" s="12" t="s">
         <v>986</v>
       </c>
@@ -34856,7 +34855,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="221" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
         <v>1218</v>
       </c>
@@ -34972,7 +34971,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="222" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A222" s="24" t="s">
         <v>754</v>
       </c>
@@ -35088,7 +35087,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="223" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A223" s="24" t="s">
         <v>761</v>
       </c>
@@ -35204,7 +35203,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="224" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A224" s="24" t="s">
         <v>763</v>
       </c>
@@ -35320,7 +35319,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="225" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A225" s="24" t="s">
         <v>765</v>
       </c>
@@ -35436,7 +35435,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="226" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A226" s="3" t="s">
         <v>320</v>
       </c>
@@ -35558,7 +35557,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="227" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A227" s="24" t="s">
         <v>754</v>
       </c>
@@ -35676,7 +35675,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="228" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A228" s="24" t="s">
         <v>761</v>
       </c>
@@ -35794,7 +35793,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="229" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A229" s="24" t="s">
         <v>763</v>
       </c>
@@ -35912,7 +35911,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="230" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A230" s="24" t="s">
         <v>765</v>
       </c>
@@ -36030,7 +36029,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="231" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
         <v>400</v>
       </c>
@@ -36150,7 +36149,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="232" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A232" s="24" t="s">
         <v>754</v>
       </c>
@@ -36268,7 +36267,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="233" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A233" s="24" t="s">
         <v>761</v>
       </c>
@@ -36386,7 +36385,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="234" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A234" s="24" t="s">
         <v>763</v>
       </c>
@@ -36504,7 +36503,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="235" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A235" s="24" t="s">
         <v>765</v>
       </c>
@@ -36622,7 +36621,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="236" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A236" s="21" t="s">
         <v>268</v>
       </c>
@@ -36742,7 +36741,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="237" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A237" s="24" t="s">
         <v>754</v>
       </c>
@@ -36860,7 +36859,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="238" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A238" s="24" t="s">
         <v>761</v>
       </c>
@@ -36978,7 +36977,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="239" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A239" s="24" t="s">
         <v>763</v>
       </c>
@@ -37096,7 +37095,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="240" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A240" s="24" t="s">
         <v>765</v>
       </c>
@@ -37214,7 +37213,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="241" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A241" s="12" t="s">
         <v>288</v>
       </c>
@@ -37334,7 +37333,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="242" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A242" s="24" t="s">
         <v>754</v>
       </c>
@@ -37452,7 +37451,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="243" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A243" s="24" t="s">
         <v>761</v>
       </c>
@@ -37570,7 +37569,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="244" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A244" s="24" t="s">
         <v>763</v>
       </c>
@@ -37688,7 +37687,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="245" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A245" s="24" t="s">
         <v>765</v>
       </c>
@@ -37806,7 +37805,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="246" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A246" s="21" t="s">
         <v>435</v>
       </c>
@@ -37926,7 +37925,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="247" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A247" s="24" t="s">
         <v>754</v>
       </c>
@@ -38044,7 +38043,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="248" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A248" s="24" t="s">
         <v>761</v>
       </c>
@@ -38162,7 +38161,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="249" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A249" s="24" t="s">
         <v>763</v>
       </c>
@@ -38280,7 +38279,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="250" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A250" s="24" t="s">
         <v>765</v>
       </c>
@@ -38398,7 +38397,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="251" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A251" s="12" t="s">
         <v>719</v>
       </c>
@@ -38518,7 +38517,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="252" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A252" s="3" t="s">
         <v>831</v>
       </c>
@@ -38632,7 +38631,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="253" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A253" s="21" t="s">
         <v>1016</v>
       </c>
@@ -38748,7 +38747,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="254" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A254" s="24" t="s">
         <v>1002</v>
       </c>
@@ -38866,7 +38865,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="255" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A255" s="36" t="s">
         <v>2065</v>
       </c>
@@ -38988,7 +38987,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="256" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A256" s="36" t="s">
         <v>2361</v>
       </c>
@@ -39110,7 +39109,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="257" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A257" s="27" t="s">
         <v>2366</v>
       </c>
@@ -39232,7 +39231,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="258" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A258" s="21" t="s">
         <v>268</v>
       </c>
@@ -39352,7 +39351,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="259" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A259" s="3" t="s">
         <v>305</v>
       </c>
@@ -39472,7 +39471,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="260" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A260" s="27" t="s">
         <v>2253</v>
       </c>
@@ -39596,7 +39595,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="261" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A261" s="27" t="s">
         <v>775</v>
       </c>
@@ -39714,7 +39713,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="262" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A262" s="3" t="s">
         <v>983</v>
       </c>
@@ -39832,7 +39831,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="263" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A263" s="36" t="s">
         <v>991</v>
       </c>
@@ -39952,7 +39951,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="264" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A264" s="24" t="s">
         <v>1002</v>
       </c>
@@ -40070,7 +40069,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="265" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A265" s="3" t="s">
         <v>1058</v>
       </c>
@@ -40194,7 +40193,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="266" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A266" s="3" t="s">
         <v>1083</v>
       </c>
@@ -40316,7 +40315,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="267" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A267" s="3" t="s">
         <v>1101</v>
       </c>
@@ -40440,7 +40439,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="268" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A268" s="3" t="s">
         <v>1121</v>
       </c>
@@ -40564,7 +40563,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="269" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A269" s="3" t="s">
         <v>1255</v>
       </c>
@@ -40686,7 +40685,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="270" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A270" s="24" t="s">
         <v>1311</v>
       </c>
@@ -40802,7 +40801,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="271" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A271" s="12" t="s">
         <v>1334</v>
       </c>
@@ -40926,7 +40925,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="272" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A272" s="27" t="s">
         <v>1402</v>
       </c>
@@ -41048,7 +41047,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="273" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A273" s="36" t="s">
         <v>1547</v>
       </c>
@@ -41168,7 +41167,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="274" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A274" s="36" t="s">
         <v>1076</v>
       </c>
@@ -41284,7 +41283,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="275" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A275" s="36" t="s">
         <v>1882</v>
       </c>
@@ -41406,7 +41405,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="276" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A276" s="36" t="s">
         <v>2072</v>
       </c>
@@ -41528,7 +41527,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="277" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A277" s="36" t="s">
         <v>2110</v>
       </c>
@@ -41650,7 +41649,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="278" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A278" s="36" t="s">
         <v>2117</v>
       </c>
@@ -41772,7 +41771,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="279" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A279" s="36" t="s">
         <v>2466</v>
       </c>
@@ -41894,7 +41893,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="280" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A280" s="21" t="s">
         <v>435</v>
       </c>
@@ -42014,7 +42013,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="281" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A281" s="12" t="s">
         <v>442</v>
       </c>
@@ -42134,7 +42133,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="282" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A282" s="36" t="s">
         <v>1572</v>
       </c>
@@ -42256,7 +42255,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="283" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A283" s="36" t="s">
         <v>1703</v>
       </c>
@@ -42378,7 +42377,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="284" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A284" s="27" t="s">
         <v>1791</v>
       </c>
@@ -42500,7 +42499,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="285" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A285" s="27" t="s">
         <v>1917</v>
       </c>
@@ -42624,7 +42623,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="286" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A286" s="36" t="s">
         <v>2330</v>
       </c>
@@ -42746,7 +42745,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="287" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A287" s="36" t="s">
         <v>2480</v>
       </c>
@@ -42868,7 +42867,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="288" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A288" s="12" t="s">
         <v>331</v>
       </c>
@@ -42988,7 +42987,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="289" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A289" s="3" t="s">
         <v>560</v>
       </c>
@@ -43108,7 +43107,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="290" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A290" s="21" t="s">
         <v>135</v>
       </c>
@@ -43230,7 +43229,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="291" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A291" s="3" t="s">
         <v>368</v>
       </c>
@@ -43352,7 +43351,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="292" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A292" s="24" t="s">
         <v>781</v>
       </c>
@@ -43470,7 +43469,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="293" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A293" s="24" t="s">
         <v>786</v>
       </c>
@@ -43588,7 +43587,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="294" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A294" s="24" t="s">
         <v>781</v>
       </c>
@@ -43706,7 +43705,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="295" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A295" s="24" t="s">
         <v>786</v>
       </c>
@@ -43824,7 +43823,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="296" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A296" s="12" t="s">
         <v>549</v>
       </c>
@@ -43946,7 +43945,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="297" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A297" s="24" t="s">
         <v>781</v>
       </c>
@@ -44064,7 +44063,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="298" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A298" s="27" t="s">
         <v>778</v>
       </c>
@@ -44182,7 +44181,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="299" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A299" s="24" t="s">
         <v>781</v>
       </c>
@@ -44300,7 +44299,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="300" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A300" s="24" t="s">
         <v>786</v>
       </c>
@@ -44418,7 +44417,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="301" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A301" s="21" t="s">
         <v>1128</v>
       </c>
@@ -44532,7 +44531,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="302" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A302" s="36" t="s">
         <v>1000</v>
       </c>
@@ -44650,7 +44649,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="303" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A303" s="21" t="s">
         <v>1128</v>
       </c>
@@ -44764,7 +44763,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="304" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A304" s="27" t="s">
         <v>988</v>
       </c>
@@ -44880,7 +44879,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="305" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A305" s="12" t="s">
         <v>1216</v>
       </c>
@@ -44996,7 +44995,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="306" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A306" s="36" t="s">
         <v>2148</v>
       </c>
@@ -45112,7 +45111,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="307" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A307" s="24" t="s">
         <v>1191</v>
       </c>
@@ -45232,7 +45231,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="308" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A308" s="24" t="s">
         <v>1199</v>
       </c>
@@ -45350,7 +45349,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="309" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A309" s="24" t="s">
         <v>1201</v>
       </c>
@@ -45468,7 +45467,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="310" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A310" s="24" t="s">
         <v>1203</v>
       </c>
@@ -45586,7 +45585,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="311" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A311" s="27" t="s">
         <v>2190</v>
       </c>
@@ -45708,7 +45707,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="312" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A312" s="12" t="s">
         <v>801</v>
       </c>
@@ -45830,7 +45829,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="313" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A313" s="27" t="s">
         <v>1168</v>
       </c>
@@ -45950,7 +45949,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="314" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A314" s="3" t="s">
         <v>1446</v>
       </c>
@@ -46074,7 +46073,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="315" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A315" s="12" t="s">
         <v>162</v>
       </c>
@@ -46194,7 +46193,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="316" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A316" s="12" t="s">
         <v>499</v>
       </c>
@@ -46314,7 +46313,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="317" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A317" s="3" t="s">
         <v>528</v>
       </c>
@@ -46434,7 +46433,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="318" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A318" s="21" t="s">
         <v>994</v>
       </c>
@@ -46550,7 +46549,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="319" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A319" s="21" t="s">
         <v>52</v>
       </c>
@@ -46670,7 +46669,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="320" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A320" s="3" t="s">
         <v>1133</v>
       </c>
@@ -46786,7 +46785,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="321" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A321" s="21" t="s">
         <v>994</v>
       </c>
@@ -46902,7 +46901,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="322" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A322" s="21" t="s">
         <v>52</v>
       </c>
@@ -47022,7 +47021,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="323" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A323" s="21" t="s">
         <v>994</v>
       </c>
@@ -47136,7 +47135,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="324" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A324" s="21" t="s">
         <v>52</v>
       </c>
@@ -47256,7 +47255,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="325" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A325" s="12" t="s">
         <v>360</v>
       </c>
@@ -47376,7 +47375,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="326" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A326" s="12" t="s">
         <v>427</v>
       </c>
@@ -47496,7 +47495,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="327" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A327" s="12" t="s">
         <v>344</v>
       </c>
@@ -47616,7 +47615,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="328" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A328" s="27" t="s">
         <v>932</v>
       </c>
@@ -47734,7 +47733,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="329" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A329" s="24" t="s">
         <v>954</v>
       </c>
@@ -47852,7 +47851,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="330" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A330" s="24" t="s">
         <v>978</v>
       </c>
@@ -47970,7 +47969,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="331" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A331" s="24" t="s">
         <v>1114</v>
       </c>
@@ -48094,7 +48093,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="332" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A332" s="12" t="s">
         <v>418</v>
       </c>
@@ -48214,7 +48213,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="333" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A333" s="24" t="s">
         <v>1324</v>
       </c>
@@ -48334,7 +48333,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="334" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A334" s="36" t="s">
         <v>947</v>
       </c>
@@ -48452,7 +48451,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="335" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A335" s="24" t="s">
         <v>960</v>
       </c>
@@ -48570,7 +48569,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="336" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A336" s="24" t="s">
         <v>970</v>
       </c>
@@ -48688,7 +48687,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="337" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A337" s="24" t="s">
         <v>972</v>
       </c>
@@ -48806,7 +48805,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="338" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A338" s="12" t="s">
         <v>1286</v>
       </c>
@@ -48924,7 +48923,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="339" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A339" s="3" t="s">
         <v>1317</v>
       </c>
@@ -49042,7 +49041,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="340" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A340" s="12" t="s">
         <v>520</v>
       </c>
@@ -49162,7 +49161,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="341" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A341" s="3" t="s">
         <v>1597</v>
       </c>
@@ -49280,7 +49279,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="342" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A342" s="12" t="s">
         <v>573</v>
       </c>
@@ -49400,7 +49399,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="343" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A343" s="12" t="s">
         <v>606</v>
       </c>
@@ -49520,7 +49519,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="344" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A344" s="12" t="s">
         <v>1868</v>
       </c>
@@ -49638,7 +49637,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="345" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A345" s="3" t="s">
         <v>1875</v>
       </c>
@@ -49756,7 +49755,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="346" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A346" s="3" t="s">
         <v>1893</v>
       </c>
@@ -49874,7 +49873,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="347" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A347" s="3" t="s">
         <v>2182</v>
       </c>
@@ -49992,7 +49991,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="348" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A348" s="36" t="s">
         <v>1473</v>
       </c>
@@ -50112,7 +50111,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="349" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A349" s="27" t="s">
         <v>1579</v>
       </c>
@@ -50232,7 +50231,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="350" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A350" s="36" t="s">
         <v>1945</v>
       </c>
@@ -50352,7 +50351,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="351" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A351" s="27" t="s">
         <v>1952</v>
       </c>
@@ -50472,7 +50471,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="352" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A352" s="36" t="s">
         <v>2035</v>
       </c>
@@ -50592,7 +50591,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="353" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A353" s="36" t="s">
         <v>2079</v>
       </c>
@@ -50712,7 +50711,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="354" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A354" s="27" t="s">
         <v>2123</v>
       </c>
@@ -50832,7 +50831,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="355" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A355" s="3" t="s">
         <v>1206</v>
       </c>
@@ -50956,7 +50955,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="356" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A356" s="27" t="s">
         <v>1352</v>
       </c>
@@ -51082,7 +51081,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="357" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A357" s="36" t="s">
         <v>1362</v>
       </c>
@@ -51208,7 +51207,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="358" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A358" s="27" t="s">
         <v>1369</v>
       </c>
@@ -51334,7 +51333,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="359" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A359" s="36" t="s">
         <v>1377</v>
       </c>
@@ -51460,7 +51459,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="360" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A360" s="27" t="s">
         <v>1386</v>
       </c>
@@ -51586,7 +51585,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="361" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A361" s="36" t="s">
         <v>1394</v>
       </c>
@@ -51712,7 +51711,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="362" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A362" s="36" t="s">
         <v>2022</v>
       </c>
@@ -51832,7 +51831,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="363" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A363" s="27" t="s">
         <v>2105</v>
       </c>
@@ -51952,7 +51951,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="364" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A364" s="27" t="s">
         <v>2430</v>
       </c>
@@ -52074,7 +52073,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="365" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A365" s="36" t="s">
         <v>2432</v>
       </c>
@@ -52194,7 +52193,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="366" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A366" s="27" t="s">
         <v>2434</v>
       </c>
@@ -52314,7 +52313,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="367" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A367" s="36" t="s">
         <v>2436</v>
       </c>
@@ -52436,7 +52435,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="368" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A368" s="27" t="s">
         <v>2442</v>
       </c>
@@ -52556,7 +52555,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="369" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A369" s="36" t="s">
         <v>2444</v>
       </c>
@@ -52678,7 +52677,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="370" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A370" s="36" t="s">
         <v>2527</v>
       </c>
@@ -52798,7 +52797,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="371" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A371" s="3" t="s">
         <v>698</v>
       </c>
@@ -52918,7 +52917,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="372" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A372" s="12" t="s">
         <v>739</v>
       </c>
@@ -53038,7 +53037,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="373" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A373" s="12" t="s">
         <v>746</v>
       </c>
@@ -53158,7 +53157,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="374" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A374" s="3" t="s">
         <v>194</v>
       </c>
@@ -53280,7 +53279,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="375" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A375" s="3" t="s">
         <v>298</v>
       </c>
@@ -53400,7 +53399,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="376" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A376" s="12" t="s">
         <v>597</v>
       </c>
@@ -53520,7 +53519,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="377" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A377" s="12" t="s">
         <v>668</v>
       </c>
@@ -53640,7 +53639,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="378" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A378" s="3" t="s">
         <v>674</v>
       </c>
@@ -53760,7 +53759,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="379" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A379" s="3" t="s">
         <v>705</v>
       </c>
@@ -53880,7 +53879,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="380" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A380" s="12" t="s">
         <v>230</v>
       </c>
@@ -54000,7 +53999,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="381" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A381" s="12" t="s">
         <v>352</v>
       </c>
@@ -54120,7 +54119,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="382" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A382" s="3" t="s">
         <v>483</v>
       </c>
@@ -54240,7 +54239,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="383" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A383" s="21" t="s">
         <v>183</v>
       </c>
@@ -54360,7 +54359,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="384" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A384" s="21" t="s">
         <v>238</v>
       </c>
@@ -54480,7 +54479,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="385" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A385" s="21" t="s">
         <v>250</v>
       </c>
@@ -54600,7 +54599,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="386" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A386" s="21" t="s">
         <v>411</v>
       </c>
@@ -54720,7 +54719,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="387" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A387" s="21" t="s">
         <v>567</v>
       </c>
@@ -54840,7 +54839,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="388" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A388" s="3" t="s">
         <v>151</v>
       </c>
@@ -54958,7 +54957,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="389" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A389" s="12" t="s">
         <v>535</v>
       </c>
@@ -55080,7 +55079,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="390" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A390" s="12" t="s">
         <v>581</v>
       </c>
@@ -55200,7 +55199,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="391" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A391" s="3" t="s">
         <v>620</v>
       </c>
@@ -55320,7 +55319,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="392" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A392" s="21" t="s">
         <v>994</v>
       </c>
@@ -55436,7 +55435,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="393" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A393" s="24" t="s">
         <v>944</v>
       </c>
@@ -55556,7 +55555,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="394" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A394" s="36" t="s">
         <v>956</v>
       </c>
@@ -55674,7 +55673,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="395" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A395" s="21" t="s">
         <v>52</v>
       </c>
@@ -55794,7 +55793,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="396" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A396" s="27" t="s">
         <v>1029</v>
       </c>
@@ -55912,7 +55911,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="397" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A397" s="36" t="s">
         <v>1034</v>
       </c>
@@ -56030,7 +56029,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="398" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A398" s="36" t="s">
         <v>1050</v>
       </c>
@@ -56150,7 +56149,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="399" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A399" s="24" t="s">
         <v>1095</v>
       </c>
@@ -56270,7 +56269,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="400" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A400" s="21" t="s">
         <v>277</v>
       </c>
@@ -56390,7 +56389,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="401" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A401" s="27" t="s">
         <v>1183</v>
       </c>
@@ -56510,7 +56509,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="402" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A402" s="21" t="s">
         <v>277</v>
       </c>
@@ -56630,7 +56629,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="403" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A403" s="21" t="s">
         <v>52</v>
       </c>
@@ -56750,7 +56749,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="404" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A404" s="24" t="s">
         <v>1324</v>
       </c>
@@ -56870,7 +56869,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="405" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A405" s="24" t="s">
         <v>1304</v>
       </c>
@@ -56990,7 +56989,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="406" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A406" s="24" t="s">
         <v>1341</v>
       </c>
@@ -57110,7 +57109,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="407" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A407" s="36" t="s">
         <v>1466</v>
       </c>
@@ -57232,7 +57231,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="408" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A408" s="36" t="s">
         <v>2128</v>
       </c>
@@ -57354,7 +57353,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="409" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A409" s="27" t="s">
         <v>2134</v>
       </c>
@@ -57476,7 +57475,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="410" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A410" s="36" t="s">
         <v>2240</v>
       </c>
@@ -57600,7 +57599,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="411" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A411" s="36" t="s">
         <v>1005</v>
       </c>
@@ -57720,7 +57719,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="412" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A412" s="3" t="s">
         <v>1014</v>
       </c>
@@ -57840,7 +57839,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="413" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A413" s="27" t="s">
         <v>1843</v>
       </c>
@@ -57962,7 +57961,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="414" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A414" s="36" t="s">
         <v>2261</v>
       </c>
@@ -58084,7 +58083,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="415" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A415" s="36" t="s">
         <v>2316</v>
       </c>
@@ -58206,7 +58205,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="416" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A416" s="27" t="s">
         <v>2392</v>
       </c>
@@ -58328,7 +58327,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="417" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A417" s="27" t="s">
         <v>2398</v>
       </c>
@@ -58450,7 +58449,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="418" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A418" s="27" t="s">
         <v>2486</v>
       </c>
@@ -58572,7 +58571,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="419" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A419" s="3" t="s">
         <v>88</v>
       </c>
@@ -58692,7 +58691,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="420" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A420" s="12" t="s">
         <v>204</v>
       </c>
@@ -58812,7 +58811,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="421" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A421" s="21" t="s">
         <v>960</v>
       </c>
@@ -58928,7 +58927,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="422" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A422" s="12" t="s">
         <v>1176</v>
       </c>
@@ -59046,7 +59045,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="423" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A423" s="12" t="s">
         <v>1185</v>
       </c>
@@ -59164,7 +59163,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="424" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A424" s="12" t="s">
         <v>102</v>
       </c>
@@ -59284,7 +59283,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="425" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A425" s="3" t="s">
         <v>589</v>
       </c>
@@ -59404,7 +59403,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="426" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A426" s="21" t="s">
         <v>183</v>
       </c>
@@ -59524,7 +59523,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="427" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A427" s="27" t="s">
         <v>1861</v>
       </c>
@@ -59646,7 +59645,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="428" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A428" s="21" t="s">
         <v>238</v>
       </c>
@@ -59766,7 +59765,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="429" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A429" s="21" t="s">
         <v>250</v>
       </c>
@@ -59886,7 +59885,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="430" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A430" s="24" t="s">
         <v>1036</v>
       </c>
@@ -60004,7 +60003,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="431" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A431" s="21" t="s">
         <v>411</v>
       </c>
@@ -60124,7 +60123,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="432" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A432" s="21" t="s">
         <v>567</v>
       </c>
@@ -60244,7 +60243,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="433" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A433" s="36" t="s">
         <v>2337</v>
       </c>
@@ -60366,7 +60365,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="434" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A434" s="12" t="s">
         <v>867</v>
       </c>
@@ -60486,7 +60485,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="435" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A435" s="36" t="s">
         <v>2506</v>
       </c>
@@ -60608,7 +60607,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="436" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A436" s="21" t="s">
         <v>872</v>
       </c>
@@ -60728,7 +60727,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="437" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A437" s="3" t="s">
         <v>874</v>
       </c>
@@ -60848,7 +60847,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="438" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A438" s="36" t="s">
         <v>1824</v>
       </c>
@@ -60970,7 +60969,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="439" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A439" s="36" t="s">
         <v>2405</v>
       </c>
@@ -61092,7 +61091,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="440" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A440" s="27" t="s">
         <v>2539</v>
       </c>
@@ -61214,7 +61213,7 @@
         <v>2546</v>
       </c>
     </row>
-    <row r="441" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A441" s="27" t="s">
         <v>2566</v>
       </c>
@@ -61336,7 +61335,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="442" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A442" s="24" t="s">
         <v>1304</v>
       </c>
@@ -61456,7 +61455,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="443" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A443" s="24" t="s">
         <v>1324</v>
       </c>
@@ -61576,7 +61575,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="444" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A444" s="24" t="s">
         <v>1618</v>
       </c>
@@ -61698,7 +61697,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="445" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A445" s="27" t="s">
         <v>1696</v>
       </c>
@@ -61820,7 +61819,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="446" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A446" s="27" t="s">
         <v>1754</v>
       </c>
@@ -61942,7 +61941,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="447" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A447" s="36" t="s">
         <v>2547</v>
       </c>
@@ -62062,7 +62061,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="448" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A448" s="36" t="s">
         <v>2584</v>
       </c>
@@ -62184,7 +62183,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="449" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A449" s="21" t="s">
         <v>880</v>
       </c>
@@ -62304,7 +62303,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="450" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A450" s="12" t="s">
         <v>886</v>
       </c>
@@ -62424,7 +62423,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="451" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A451" s="21" t="s">
         <v>890</v>
       </c>
@@ -62544,7 +62543,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="452" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A452" s="27" t="s">
         <v>2356</v>
       </c>
@@ -62664,7 +62663,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="453" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A453" s="24" t="s">
         <v>1304</v>
       </c>
@@ -62784,7 +62783,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="454" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A454" s="24" t="s">
         <v>1341</v>
       </c>
@@ -62904,7 +62903,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="455" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A455" s="36" t="s">
         <v>2198</v>
       </c>
@@ -63026,7 +63025,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="456" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A456" s="24" t="s">
         <v>1304</v>
       </c>
@@ -63146,7 +63145,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="457" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A457" s="27" t="s">
         <v>1804</v>
       </c>
@@ -63266,7 +63265,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="458" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A458" s="24" t="s">
         <v>1304</v>
       </c>
@@ -63386,7 +63385,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="459" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A459" s="21" t="s">
         <v>892</v>
       </c>
@@ -63506,7 +63505,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="460" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A460" s="24" t="s">
         <v>1625</v>
       </c>
@@ -63626,7 +63625,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="461" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A461" s="24" t="s">
         <v>1625</v>
       </c>
@@ -63748,7 +63747,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="462" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A462" s="24" t="s">
         <v>1341</v>
       </c>
@@ -63868,7 +63867,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="463" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A463" s="36" t="s">
         <v>1418</v>
       </c>
@@ -63988,7 +63987,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="464" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A464" s="24" t="s">
         <v>1618</v>
       </c>
@@ -64110,7 +64109,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="465" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A465" s="36" t="s">
         <v>1855</v>
       </c>
@@ -64230,7 +64229,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="466" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A466" s="24" t="s">
         <v>2323</v>
       </c>
@@ -64352,7 +64351,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="467" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A467" s="27" t="s">
         <v>2533</v>
       </c>
@@ -64474,7 +64473,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="468" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A468" s="21" t="s">
         <v>896</v>
       </c>
@@ -64594,7 +64593,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="469" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A469" s="21" t="s">
         <v>903</v>
       </c>
@@ -64714,7 +64713,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="470" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A470" s="21" t="s">
         <v>910</v>
       </c>
@@ -64834,7 +64833,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="471" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A471" s="21" t="s">
         <v>913</v>
       </c>
@@ -64950,7 +64949,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="472" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A472" s="24" t="s">
         <v>1036</v>
       </c>
@@ -65068,7 +65067,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="473" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A473" s="21" t="s">
         <v>920</v>
       </c>
@@ -65188,7 +65187,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="474" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A474" s="21" t="s">
         <v>930</v>
       </c>
@@ -65308,7 +65307,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="475" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A475" s="27" t="s">
         <v>844</v>
       </c>
@@ -65430,7 +65429,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="476" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A476" s="36" t="s">
         <v>847</v>
       </c>
@@ -65554,7 +65553,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="477" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A477" s="24" t="s">
         <v>1304</v>
       </c>
@@ -65674,7 +65673,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="478" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A478" s="24" t="s">
         <v>1324</v>
       </c>
@@ -65794,7 +65793,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="479" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A479" s="27" t="s">
         <v>2411</v>
       </c>
@@ -65916,7 +65915,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="480" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A480" s="36" t="s">
         <v>2493</v>
       </c>
@@ -66038,7 +66037,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="481" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A481" s="36" t="s">
         <v>2579</v>
       </c>
@@ -66158,7 +66157,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="482" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A482" s="21" t="s">
         <v>1016</v>
       </c>
@@ -66274,7 +66273,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="483" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A483" s="12" t="s">
         <v>789</v>
       </c>
@@ -66394,7 +66393,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="484" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A484" s="3" t="s">
         <v>794</v>
       </c>
@@ -66514,7 +66513,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="485" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A485" s="3" t="s">
         <v>75</v>
       </c>
@@ -66634,7 +66633,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="486" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A486" s="3" t="s">
         <v>808</v>
       </c>
@@ -66754,7 +66753,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="487" spans="1:42" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A487" s="12" t="s">
         <v>810</v>
       </c>
@@ -66876,7 +66875,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="488" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A488" s="12" t="s">
         <v>115</v>
       </c>
@@ -66996,7 +66995,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="489" spans="1:42" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A489" s="23"/>
       <c r="B489" s="23"/>
       <c r="C489" s="23"/>
@@ -67041,35 +67040,7 @@
       <c r="AP489" s="23"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP488" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <colorFilter dxfId="0" cellColor="0"/>
-    </filterColumn>
-    <filterColumn colId="33">
-      <filters blank="1">
-        <filter val="SHIP VIA EFWW-ESTES FORWARDING WW"/>
-        <filter val="SHIP VIA FEDERAL EX-GROUND"/>
-        <filter val="SHIP VIA FEDERAL EX-STANDARD GROUND"/>
-        <filter val="SHIP VIA FEDEX GND"/>
-        <filter val="SHIP VIA FEDEX HOME DELIVERY"/>
-        <filter val="SHIP VIA FEDEX HOME DELIVERY FEDH"/>
-        <filter val="SHIP VIA FEDEX HOME DELV"/>
-        <filter val="SHIP VIA Ground"/>
-        <filter val="SHIP VIA UNKNOWN-CALL EDI-98"/>
-        <filter val="SHIP VIA UPS GROUND"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="37">
-      <filters blank="1">
-        <filter val="FXGR"/>
-        <filter val="UPS2"/>
-        <filter val="UPSS"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:AP488">
-      <sortCondition ref="G1:G488"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:AP488" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
